--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-statistics-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-statistics-easy.xlsx
@@ -492,19 +492,19 @@
         <v>Trong phân phối lệch (skewed distribution), trung bình cộng (Mean) bị ảnh hưởng mạnh bởi các outliers. Trung vị (Median) giữ nguyên tính chất phân vị 50% nên phản ánh trung thực hơn.</v>
       </c>
       <c r="F3" t="str">
+        <v>Yếu vị (Mode) — chỉ phản ánh mức lương có số lượng người nhận nhiều nhất cụ thể</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Độ lệch chuẩn (Standard Deviation) — chỉ đo lường mức độ biến động chứ không phản ánh giá trị trung tâm</v>
+      </c>
+      <c r="H3" t="str">
         <v>Trung vị (Median) — không bị bóp méo bởi một số ít giá trị cực trị (outliers) quá lớn</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>Trung bình cộng (Mean) — bị kéo lệch lên cao bởi những người cực giàu</v>
       </c>
-      <c r="H3" t="str">
-        <v>Yếu vị (Mode) — chỉ phản ánh mức lương có số lượng người nhận nhiều nhất cụ thể</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Độ lệch chuẩn (Standard Deviation) — chỉ đo lường mức độ biến động chứ không phản ánh giá trị trung tâm</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -527,13 +527,13 @@
         <v>Mức độ phân tán của các điểm dữ liệu xung quanh giá trị trung bình cộng của chúng — độ biến động dữ liệu</v>
       </c>
       <c r="G4" t="str">
+        <v>Tần suất xuất hiện trung bình của các giá trị trùng lặp trong tập dữ liệu</v>
+      </c>
+      <c r="H4" t="str">
         <v>Mức độ tương quan tuyến tính giữa hai biến số độc lập với nhau</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>Giá trị trung bình của khoảng cách giữa giá trị lớn nhất và nhỏ nhất</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Tần suất xuất hiện trung bình của các giá trị trùng lặp trong tập dữ liệu</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -556,19 +556,19 @@
         <v>Correlation không có nghĩa là Causation. Hai biến có thể tương quan mạnh do cùng phụ thuộc vào một biến thứ ba (confounding variable), chứ không trực tiếp gây ra nhau.</v>
       </c>
       <c r="F5" t="str">
+        <v>Tương quan chỉ áp dụng cho số liệu kinh tế; Nhân quả chỉ áp dụng cho số liệu y học</v>
+      </c>
+      <c r="G5" t="str">
         <v>Tương quan chỉ ra hai biến biến đổi cùng nhau; Nhân quả khẳng định sự thay đổi của biến này trực tiếp tạo ra sự thay đổi của biến kia</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Tương quan bắt buộc phải có giá trị âm; Nhân quả bắt buộc phải có giá trị dương</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Tương quan chỉ áp dụng cho số liệu kinh tế; Nhân quả chỉ áp dụng cho số liệu y học</v>
       </c>
       <c r="I5" t="str">
         <v>Tương quan là mối quan hệ chắc chắn 100%; Nhân quả chỉ là giả thuyết thống kê</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -591,10 +591,10 @@
         <v>Biểu đồ đường (Line Chart) — thể hiện xu hướng liên tục và sự thay đổi theo tiến trình thời gian</v>
       </c>
       <c r="G6" t="str">
+        <v>Biểu đồ phân tán (Scatter Plot) — thể hiện mối quan hệ và sự phân bố giữa hai biến số</v>
+      </c>
+      <c r="H6" t="str">
         <v>Biểu đồ tròn (Pie Chart) — thể hiện tỷ lệ phần trăm đóng góp của các phần trong tổng thể tĩnh</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Biểu đồ phân tán (Scatter Plot) — thể hiện mối quan hệ và sự phân bố giữa hai biến số</v>
       </c>
       <c r="I6" t="str">
         <v>Biểu đồ bản đồ nhiệt (Heatmap) — thể hiện mật độ dữ liệu thông qua màu sắc tương phản</v>
@@ -620,19 +620,19 @@
         <v>Pie chart chỉ hiệu quả khi so sánh các phần của một tổng thể (phải cộng lại bằng 100%) và có ít danh mục. Có quá nhiều lát cắt sẽ khiến biểu đồ cực kỳ khó đọc.</v>
       </c>
       <c r="F7" t="str">
+        <v>Trực quan hóa sự biến động của giá cổ phiếu liên tục trong vòng 30 ngày</v>
+      </c>
+      <c r="G7" t="str">
         <v>So sánh tỷ lệ phần trăm đóng góp của một số ít danh mục (dưới 5) cấu thành nên một tổng thể 100%</v>
       </c>
-      <c r="G7" t="str">
-        <v>Trực quan hóa sự biến động của giá cổ phiếu liên tục trong vòng 30 ngày</v>
-      </c>
       <c r="H7" t="str">
+        <v>Thể hiện sự phân bố tần suất của các nhóm tuổi học sinh trong một trường học</v>
+      </c>
+      <c r="I7" t="str">
         <v>So sánh doanh thu của 50 chi nhánh cửa hàng khác nhau trên toàn quốc</v>
       </c>
-      <c r="I7" t="str">
-        <v>Thể hiện sự phân bố tần suất của các nhóm tuổi học sinh trong một trường học</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -658,10 +658,10 @@
         <v>Tỷ lệ phần trăm dữ liệu bị lỗi hoặc khuyết thiếu trong tập dữ liệu thử nghiệm</v>
       </c>
       <c r="H8" t="str">
+        <v>Mức độ chênh lệch giữa giá trị trung bình và giá trị trung vị của tập dữ liệu</v>
+      </c>
+      <c r="I8" t="str">
         <v>Độ tin cậy của mô hình dự báo tuyến tính khi số lượng quan sát tăng lên</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Mức độ chênh lệch giữa giá trị trung bình và giá trị trung vị của tập dữ liệu</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>Hướng đi lên thể hiện mối quan hệ đồng biến (tương quan dương). Độ dốc và khoảng cách các điểm đến đường thẳng xu hướng thể hiện độ mạnh yếu của tương quan.</v>
       </c>
       <c r="F9" t="str">
+        <v>Mối quan hệ tương quan âm (Negative Correlation) giữa hai biến số — biến X tăng thì biến Y giảm</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Không tồn tại bất kỳ mối liên hệ nào giữa hai biến số đang xét</v>
+      </c>
+      <c r="H9" t="str">
         <v>Mối quan hệ tương quan dương (Positive Correlation) giữa hai biến số — biến X tăng thì biến Y cũng có xu hướng tăng</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Mối quan hệ tương quan âm (Negative Correlation) giữa hai biến số — biến X tăng thì biến Y giảm</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Không tồn tại bất kỳ mối liên hệ nào giữa hai biến số đang xét</v>
       </c>
       <c r="I9" t="str">
         <v>Dữ liệu bị lỗi thu thập dẫn đến phân phối không đều</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Conversion Rate đo lường tỷ lệ người dùng thực hiện một hành động mong muốn (mua hàng, đăng ký) trên tổng số người tiếp cận.</v>
       </c>
       <c r="F10" t="str">
-        <v>(Số khách hàng thực hiện mua hàng / Tổng số khách hàng truy cập trang web) * 100% — đo lường hiệu quả bán hàng</v>
+        <v>(Số lượng người dùng rời bỏ trang web / Tổng số tài khoản đăng ký mới) * 100% — tính tỷ lệ churn rate</v>
       </c>
       <c r="G10" t="str">
         <v>(Số tiền doanh thu thu được / Tổng số lượng sản phẩm đã bán ra) * 100% — tính giá trị trung bình đơn</v>
       </c>
       <c r="H10" t="str">
+        <v>(Số khách hàng thực hiện mua hàng / Tổng số khách hàng truy cập trang web) * 100% — đo lường hiệu quả bán hàng</v>
+      </c>
+      <c r="I10" t="str">
         <v>(Số lượt click vào quảng cáo / Tổng số lượt hiển thị quảng cáo) * 100% — tính tỷ lệ CTR của quảng cáo</v>
       </c>
-      <c r="I10" t="str">
-        <v>(Số lượng người dùng rời bỏ trang web / Tổng số tài khoản đăng ký mới) * 100% — tính tỷ lệ churn rate</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -751,13 +751,13 @@
         <v>Khi nó khác biệt quá lớn (nằm quá xa) so với phần lớn các quan sát khác trong tập dữ liệu — giá trị cực trị bất thường</v>
       </c>
       <c r="G11" t="str">
+        <v>Khi nó xuất hiện nhiều lần liên tiếp trong cùng một cột dữ liệu</v>
+      </c>
+      <c r="H11" t="str">
         <v>Khi nó bị khuyết thiếu (NULL) trong cơ sở dữ liệu quan hệ</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>Khi nó chứa các ký tự chữ cái nằm trong cột được định nghĩa kiểu dữ liệu số</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Khi nó xuất hiện nhiều lần liên tiếp trong cùng một cột dữ liệu</v>
       </c>
       <c r="J11">
         <v>1</v>
